--- a/human_resources_forms/034_employment_opportunities_feedback_survey_form--human_resources_forms.xlsx
+++ b/human_resources_forms/034_employment_opportunities_feedback_survey_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very high'}</t>
+          <t>Very high</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_high'}</t>
+          <t>somewhat_high</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat high'}</t>
+          <t>Somewhat high</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_high'}</t>
+          <t>not_very_high</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Not very high'}</t>
+          <t>Not very high</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'from_website'}</t>
+          <t>from_website</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'From website'}</t>
+          <t>From website</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'from_a_friend_or_colleague'}</t>
+          <t>from_a_friend_or_colleague</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'From a friend or colleague'}</t>
+          <t>From a friend or colleague</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'from_a_job_ad'}</t>
+          <t>from_a_job_ad</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'From a job ad'}</t>
+          <t>From a job ad</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
